--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1881.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1881.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5517512F-6BDD-4FC9-AE64-0A4E141B95ED}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5682B5A2-7BD1-49F4-A16F-85033710EFE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3210" yWindow="1695" windowWidth="23610" windowHeight="20055" xr2:uid="{985C1713-17F3-42B8-B4A8-3581E02B593F}"/>
+    <workbookView xWindow="63390" yWindow="2085" windowWidth="27480" windowHeight="15000" activeTab="1" xr2:uid="{985C1713-17F3-42B8-B4A8-3581E02B593F}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="2" r:id="rId1"/>
     <sheet name="Data" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +24,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -409,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -441,7 +446,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -461,9 +465,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -501,7 +505,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -607,7 +611,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -749,7 +753,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -758,29 +762,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF2DD7B-2B66-4003-BA93-F7F267E7D338}">
   <dimension ref="A2:A10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>105</v>
       </c>
@@ -793,22 +797,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3A086F-87DA-488B-9CB2-83FFAA408376}">
   <dimension ref="A1:R90"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="27.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" style="3" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="3"/>
-    <col min="5" max="6" width="9.140625" style="8"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="13"/>
-    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.578125" customWidth="1"/>
+    <col min="2" max="2" width="10.578125" style="3" customWidth="1"/>
+    <col min="3" max="4" width="9.15625" style="3"/>
+    <col min="5" max="6" width="9.15625" style="8"/>
+    <col min="8" max="8" width="10.15625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.15625" style="13"/>
+    <col min="14" max="14" width="13.41796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.41796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.15625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.41796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.15625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
@@ -858,7 +862,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -898,7 +902,7 @@
         <v>6.4621852996302298E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -938,7 +942,7 @@
         <v>1.5648635960596735E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -978,7 +982,7 @@
         <v>-7.9391594710933155E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1018,7 +1022,7 @@
         <v>-5.9488167727879127E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1044,7 +1048,7 @@
       <c r="Q7" s="14"/>
       <c r="R7" s="14"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1084,7 +1088,7 @@
         <v>-6.4077109624486983E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1124,7 +1128,7 @@
         <v>-6.2556476798931726E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1164,7 +1168,7 @@
         <v>-6.7792311172494291E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1204,7 +1208,7 @@
         <v>-3.9114158342520966E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1244,7 +1248,7 @@
         <v>-1.7026883984650354E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1284,7 +1288,7 @@
         <v>-5.2409346527597656E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>74</v>
       </c>
@@ -1324,7 +1328,7 @@
         <v>1.5193626088576551E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1364,7 +1368,7 @@
         <v>-7.2407922601005037E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1404,7 +1408,7 @@
         <v>-2.9304792636075661E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1444,7 +1448,7 @@
         <v>-1.4510509501377555E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -1484,7 +1488,7 @@
         <v>-1.1795193441895169E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1524,7 +1528,7 @@
         <v>-8.7982211672398503E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>75</v>
       </c>
@@ -1564,7 +1568,7 @@
         <v>-8.4286839743246134E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1604,7 +1608,7 @@
         <v>7.6332796613987064E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1644,7 +1648,7 @@
         <v>-9.9232695759414291E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -1684,7 +1688,7 @@
         <v>-1.4771780717482308E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1724,7 +1728,7 @@
         <v>-8.0356024760047884E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -1764,7 +1768,7 @@
         <v>-7.9176108302829507E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -1804,7 +1808,7 @@
         <v>0.46357055846046258</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -1844,7 +1848,7 @@
         <v>-9.1161700376274801E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>76</v>
       </c>
@@ -1884,7 +1888,7 @@
         <v>-7.4644868004774434E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>77</v>
       </c>
@@ -1924,7 +1928,7 @@
         <v>-6.5395943102370513E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -1964,7 +1968,7 @@
         <v>-7.3330450892743038E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -2004,7 +2008,7 @@
         <v>-8.4966798785195863E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -2044,7 +2048,7 @@
         <v>-9.7624660147951126E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -2084,7 +2088,7 @@
         <v>-1.106652597788127E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -2124,7 +2128,7 @@
         <v>-7.3149572427606557E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -2164,7 +2168,7 @@
         <v>-9.5450477231835862E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -2204,7 +2208,7 @@
         <v>-8.5310106530416707E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -2244,7 +2248,7 @@
         <v>-4.9927264684899164E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -2284,7 +2288,7 @@
         <v>-5.0298802600567516E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -2324,7 +2328,7 @@
         <v>-3.7839462007159153E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -2364,7 +2368,7 @@
         <v>-8.5437105761511756E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>34</v>
       </c>
@@ -2404,7 +2408,7 @@
         <v>-6.2143118993441604E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -2444,7 +2448,7 @@
         <v>-4.7704337365501726E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -2484,7 +2488,7 @@
         <v>-0.21075836777658541</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -2524,7 +2528,7 @@
         <v>-7.7954086287725488E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -2564,7 +2568,7 @@
         <v>-4.5993392554171564E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -2604,7 +2608,7 @@
         <v>-9.7557783778566609E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>79</v>
       </c>
@@ -2644,7 +2648,7 @@
         <v>-4.1697897352950264E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -2684,7 +2688,7 @@
         <v>-2.6455651113114875E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>40</v>
       </c>
@@ -2724,7 +2728,7 @@
         <v>-4.4627112417340076E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>41</v>
       </c>
@@ -2764,7 +2768,7 @@
         <v>-1.5704937537179831E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>42</v>
       </c>
@@ -2804,7 +2808,7 @@
         <v>-2.355671059959219E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>101</v>
       </c>
@@ -2821,7 +2825,7 @@
       <c r="Q52" s="14"/>
       <c r="R52" s="14"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>43</v>
       </c>
@@ -2834,7 +2838,7 @@
       <c r="D53" s="3">
         <v>79092</v>
       </c>
-      <c r="E53" s="16">
+      <c r="E53" s="15">
         <v>4.9000000000000004</v>
       </c>
       <c r="F53" s="8">
@@ -2861,7 +2865,7 @@
         <v>-6.922364564697725E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>44</v>
       </c>
@@ -2901,7 +2905,7 @@
         <v>-4.4445007495040656E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>45</v>
       </c>
@@ -2941,7 +2945,7 @@
         <v>-4.4231140514589207E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>80</v>
       </c>
@@ -2981,7 +2985,7 @@
         <v>-7.6486387012702828E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>46</v>
       </c>
@@ -3021,7 +3025,7 @@
         <v>-3.5640210233049974E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>47</v>
       </c>
@@ -3037,7 +3041,7 @@
       <c r="E58" s="8">
         <v>4.8</v>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="15">
         <v>2.6</v>
       </c>
       <c r="G58" s="3"/>
@@ -3061,7 +3065,7 @@
         <v>-4.5776529337008043E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>48</v>
       </c>
@@ -3101,7 +3105,7 @@
         <v>-9.6082597674744363E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>49</v>
       </c>
@@ -3141,7 +3145,7 @@
         <v>-3.6106044022862882E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -3181,7 +3185,7 @@
         <v>-6.8140652929852941E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>51</v>
       </c>
@@ -3221,7 +3225,7 @@
         <v>-9.1829919857522313E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>52</v>
       </c>
@@ -3261,7 +3265,7 @@
         <v>-7.817962628089159E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>53</v>
       </c>
@@ -3301,7 +3305,7 @@
         <v>-1.3044417705822209E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>54</v>
       </c>
@@ -3341,7 +3345,7 @@
         <v>-9.5513788005523903E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>55</v>
       </c>
@@ -3381,7 +3385,7 @@
         <v>-3.7697612089531152E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>81</v>
       </c>
@@ -3421,7 +3425,7 @@
         <v>-2.6566552318809222E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>56</v>
       </c>
@@ -3461,7 +3465,7 @@
         <v>-3.0064206244179381E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>57</v>
       </c>
@@ -3501,7 +3505,7 @@
         <v>-6.8440091177950801E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>58</v>
       </c>
@@ -3562,13 +3566,13 @@
         <v>1.4909210494805425E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>59</v>
       </c>
@@ -3592,7 +3596,7 @@
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>60</v>
       </c>
@@ -3616,7 +3620,7 @@
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>61</v>
       </c>
@@ -3640,7 +3644,7 @@
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -3664,7 +3668,7 @@
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>62</v>
       </c>
@@ -3688,7 +3692,7 @@
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>83</v>
       </c>
@@ -3712,7 +3716,7 @@
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>84</v>
       </c>
@@ -3736,7 +3740,7 @@
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>63</v>
       </c>
@@ -3760,7 +3764,7 @@
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>64</v>
       </c>
@@ -3784,7 +3788,7 @@
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>65</v>
       </c>
@@ -3808,7 +3812,7 @@
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>66</v>
       </c>
@@ -3832,7 +3836,7 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>67</v>
       </c>
@@ -3893,13 +3897,13 @@
         <v>0.9127540625225522</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>68</v>
       </c>
@@ -3922,7 +3926,7 @@
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>69</v>
       </c>
@@ -3945,12 +3949,12 @@
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="G87" s="3"/>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -3999,15 +4003,15 @@
         <f>D88-J88</f>
         <v>0</v>
       </c>
-      <c r="Q88" s="15"/>
-      <c r="R88" s="15"/>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q88" s="8"/>
+      <c r="R88" s="8"/>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="G89" s="3"/>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>102</v>
       </c>
@@ -4072,4 +4076,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1881.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1881.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5682B5A2-7BD1-49F4-A16F-85033710EFE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="63390" yWindow="2085" windowWidth="27480" windowHeight="15000" activeTab="1" xr2:uid="{985C1713-17F3-42B8-B4A8-3581E02B593F}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{985C1713-17F3-42B8-B4A8-3581E02B593F}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="2" r:id="rId1"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1881.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1881.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5682B5A2-7BD1-49F4-A16F-85033710EFE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476B1074-6EE1-47D7-B94C-49518827F45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{985C1713-17F3-42B8-B4A8-3581E02B593F}"/>
+    <workbookView xWindow="82620" yWindow="1380" windowWidth="20655" windowHeight="16800" activeTab="1" xr2:uid="{985C1713-17F3-42B8-B4A8-3581E02B593F}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="111">
   <si>
     <t>Архангельская</t>
   </si>
@@ -243,12 +243,6 @@
     <t>Итого  в областях</t>
   </si>
   <si>
-    <t>Севастополь</t>
-  </si>
-  <si>
-    <t>Керчь-Еникольское град.</t>
-  </si>
-  <si>
     <t>губ</t>
   </si>
   <si>
@@ -315,9 +309,6 @@
     <t>v-diff-чс YY</t>
   </si>
   <si>
-    <t>Итого в градоначальствах</t>
-  </si>
-  <si>
     <t>р YY</t>
   </si>
   <si>
@@ -345,9 +336,6 @@
     <t>С-Петербург  пригороды</t>
   </si>
   <si>
-    <t>Итого в Империи без гр.</t>
-  </si>
-  <si>
     <t>Строка "итого" исключает число рождений и смертей в Варшаве.</t>
   </si>
   <si>
@@ -355,6 +343,33 @@
   </si>
   <si>
     <t>Прим. Вост. Сибири = Приморская обл.</t>
+  </si>
+  <si>
+    <t>необходимо прибавить к Санкт-Петербургской губернии</t>
+  </si>
+  <si>
+    <t>градоначалия</t>
+  </si>
+  <si>
+    <t>уже включены в соответствующие губернии</t>
+  </si>
+  <si>
+    <t>[Севастополь]</t>
+  </si>
+  <si>
+    <t>[Керчь-Еникольское град.]</t>
+  </si>
+  <si>
+    <t>[Итого в градоначальствах]</t>
+  </si>
+  <si>
+    <t>[Итого в Империи без гр.]</t>
+  </si>
+  <si>
+    <t>С-Петербург пригороды</t>
+  </si>
+  <si>
+    <t>добавить к</t>
   </si>
 </sst>
 </file>
@@ -414,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -447,6 +462,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -761,32 +777,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF2DD7B-2B66-4003-BA93-F7F267E7D338}">
-  <dimension ref="A2:A10"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
+      <c r="D15" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -796,73 +828,77 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3A086F-87DA-488B-9CB2-83FFAA408376}">
-  <dimension ref="A1:R90"/>
+  <dimension ref="A1:S90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="27.578125" customWidth="1"/>
     <col min="2" max="2" width="10.578125" style="3" customWidth="1"/>
     <col min="3" max="4" width="9.15625" style="3"/>
     <col min="5" max="6" width="9.15625" style="8"/>
-    <col min="8" max="8" width="10.15625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.15625" style="13"/>
-    <col min="14" max="14" width="13.41796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.41796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.15625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.41796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.15625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.89453125" style="8" customWidth="1"/>
+    <col min="9" max="9" width="10.15625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.15625" style="13"/>
+    <col min="15" max="15" width="13.41796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.41796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.15625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.41796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.15625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="E1" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="M1" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="O1" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="R1" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="12" t="s">
+      <c r="S1" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q1" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="R1" s="12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -881,28 +917,28 @@
       <c r="F3" s="8">
         <v>2.7</v>
       </c>
-      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="13">
+      <c r="K3" s="3"/>
+      <c r="L3" s="13">
         <f>100*C3/B3</f>
         <v>3.6586292487715921</v>
       </c>
-      <c r="L3" s="13">
+      <c r="M3" s="13">
         <f>D3/B3*100</f>
         <v>2.6353781470036979</v>
       </c>
-      <c r="Q3" s="14">
-        <f>E3-K3</f>
+      <c r="R3" s="14">
+        <f>E3-L3</f>
         <v>-5.8629248771592035E-2</v>
       </c>
-      <c r="R3" s="14">
-        <f>F3-L3</f>
+      <c r="S3" s="14">
+        <f>F3-M3</f>
         <v>6.4621852996302298E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -921,28 +957,28 @@
       <c r="F4" s="8">
         <v>1.8</v>
       </c>
-      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="13">
-        <f t="shared" ref="K4:K68" si="0">100*C4/B4</f>
+      <c r="K4" s="3"/>
+      <c r="L4" s="13">
+        <f t="shared" ref="L4:L68" si="0">100*C4/B4</f>
         <v>3.0409211830368785</v>
       </c>
-      <c r="L4" s="13">
-        <f t="shared" ref="L4:L68" si="1">D4/B4*100</f>
+      <c r="M4" s="13">
+        <f t="shared" ref="M4:M68" si="1">D4/B4*100</f>
         <v>1.7999843513640394</v>
       </c>
-      <c r="Q4" s="14">
-        <f t="shared" ref="Q4:Q68" si="2">E4-K4</f>
+      <c r="R4" s="14">
+        <f t="shared" ref="R4:R68" si="2">E4-L4</f>
         <v>-4.0921183036878528E-2</v>
       </c>
-      <c r="R4" s="14">
-        <f t="shared" ref="R4:R68" si="3">F4-L4</f>
+      <c r="S4" s="14">
+        <f t="shared" ref="S4:S68" si="3">F4-M4</f>
         <v>1.5648635960596735E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -961,28 +997,28 @@
       <c r="F5" s="8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="13">
+      <c r="K5" s="3"/>
+      <c r="L5" s="13">
         <f t="shared" si="0"/>
         <v>4.7623721258295753</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <f t="shared" si="1"/>
         <v>2.379391594710933</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="R5" s="14">
         <f t="shared" si="2"/>
         <v>-6.2372125829575076E-2</v>
       </c>
-      <c r="R5" s="14">
+      <c r="S5" s="14">
         <f t="shared" si="3"/>
         <v>-7.9391594710933155E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1001,28 +1037,28 @@
       <c r="F6" s="8">
         <v>2.6</v>
       </c>
-      <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="13">
+      <c r="K6" s="3"/>
+      <c r="L6" s="13">
         <f t="shared" si="0"/>
         <v>3.7561297030260286</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <f t="shared" si="1"/>
         <v>2.6594881677278792</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="R6" s="14">
         <f t="shared" si="2"/>
         <v>-5.6129703026028377E-2</v>
       </c>
-      <c r="R6" s="14">
+      <c r="S6" s="14">
         <f t="shared" si="3"/>
         <v>-5.9488167727879127E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1036,19 +1072,20 @@
         <v>11483</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G7" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="G7" s="9"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="Q7" s="14"/>
+      <c r="K7" s="3"/>
       <c r="R7" s="14"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="S7" s="14"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1067,28 +1104,28 @@
       <c r="F8" s="8">
         <v>3.1</v>
       </c>
-      <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="13">
+      <c r="K8" s="3"/>
+      <c r="L8" s="13">
         <f t="shared" si="0"/>
         <v>4.0154916491650861</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <f t="shared" si="1"/>
         <v>3.1640771096244871</v>
       </c>
-      <c r="Q8" s="14">
+      <c r="R8" s="14">
         <f t="shared" si="2"/>
         <v>-1.5491649165086052E-2</v>
       </c>
-      <c r="R8" s="14">
+      <c r="S8" s="14">
         <f t="shared" si="3"/>
         <v>-6.4077109624486983E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1107,28 +1144,28 @@
       <c r="F9" s="8">
         <v>2.6</v>
       </c>
-      <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="13">
+      <c r="K9" s="3"/>
+      <c r="L9" s="13">
         <f t="shared" si="0"/>
         <v>4.0313645499206459</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <f t="shared" si="1"/>
         <v>2.6062556476798933</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="R9" s="14">
         <f t="shared" si="2"/>
         <v>-3.1364549920645857E-2</v>
       </c>
-      <c r="R9" s="14">
+      <c r="S9" s="14">
         <f t="shared" si="3"/>
         <v>-6.2556476798931726E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1147,28 +1184,28 @@
       <c r="F10" s="8">
         <v>3.7</v>
       </c>
-      <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="13">
+      <c r="K10" s="3"/>
+      <c r="L10" s="13">
         <f t="shared" si="0"/>
         <v>5.2174878751040685</v>
       </c>
-      <c r="L10" s="13">
+      <c r="M10" s="13">
         <f t="shared" si="1"/>
         <v>3.7677923111724945</v>
       </c>
-      <c r="Q10" s="14">
+      <c r="R10" s="14">
         <f t="shared" si="2"/>
         <v>-1.7487875104068351E-2</v>
       </c>
-      <c r="R10" s="14">
+      <c r="S10" s="14">
         <f t="shared" si="3"/>
         <v>-6.7792311172494291E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1187,28 +1224,28 @@
       <c r="F11" s="8">
         <v>3.9</v>
       </c>
-      <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="13">
+      <c r="K11" s="3"/>
+      <c r="L11" s="13">
         <f t="shared" si="0"/>
         <v>4.7462205232137711</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <f t="shared" si="1"/>
         <v>3.9391141583425209</v>
       </c>
-      <c r="Q11" s="14">
+      <c r="R11" s="14">
         <f t="shared" si="2"/>
         <v>-4.6220523213770903E-2</v>
       </c>
-      <c r="R11" s="14">
+      <c r="S11" s="14">
         <f t="shared" si="3"/>
         <v>-3.9114158342520966E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1227,28 +1264,28 @@
       <c r="F12" s="8">
         <v>3.5</v>
       </c>
-      <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="13">
+      <c r="K12" s="3"/>
+      <c r="L12" s="13">
         <f t="shared" si="0"/>
         <v>4.6670424373528512</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <f t="shared" si="1"/>
         <v>3.5170268839846504</v>
       </c>
-      <c r="Q12" s="14">
+      <c r="R12" s="14">
         <f t="shared" si="2"/>
         <v>-6.7042437352851536E-2</v>
       </c>
-      <c r="R12" s="14">
+      <c r="S12" s="14">
         <f t="shared" si="3"/>
         <v>-1.7026883984650354E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1267,30 +1304,30 @@
       <c r="F13" s="8">
         <v>3.6</v>
       </c>
-      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="13">
+      <c r="K13" s="3"/>
+      <c r="L13" s="13">
         <f t="shared" si="0"/>
         <v>5.1830798456291571</v>
       </c>
-      <c r="L13" s="13">
+      <c r="M13" s="13">
         <f t="shared" si="1"/>
         <v>3.6052409346527599</v>
       </c>
-      <c r="Q13" s="14">
+      <c r="R13" s="14">
         <f t="shared" si="2"/>
         <v>-8.3079845629157489E-2</v>
       </c>
-      <c r="R13" s="14">
+      <c r="S13" s="14">
         <f t="shared" si="3"/>
         <v>-5.2409346527597656E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B14" s="3">
         <v>2698500</v>
@@ -1307,28 +1344,28 @@
       <c r="F14" s="8">
         <v>4.2</v>
       </c>
-      <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="13">
+      <c r="K14" s="3"/>
+      <c r="L14" s="13">
         <f t="shared" si="0"/>
         <v>5.6827126181211787</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <f t="shared" si="1"/>
         <v>4.1984806373911425</v>
       </c>
-      <c r="Q14" s="14">
+      <c r="R14" s="14">
         <f t="shared" si="2"/>
         <v>-8.2712618121179027E-2</v>
       </c>
-      <c r="R14" s="14">
+      <c r="S14" s="14">
         <f t="shared" si="3"/>
         <v>1.5193626088576551E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1347,28 +1384,28 @@
       <c r="F15" s="8">
         <v>3.4</v>
       </c>
-      <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="13">
+      <c r="K15" s="3"/>
+      <c r="L15" s="13">
         <f t="shared" si="0"/>
         <v>4.1039737574222483</v>
       </c>
-      <c r="L15" s="13">
+      <c r="M15" s="13">
         <f t="shared" si="1"/>
         <v>3.4724079226010049</v>
       </c>
-      <c r="Q15" s="14">
+      <c r="R15" s="14">
         <f t="shared" si="2"/>
         <v>-3.9737574222487027E-3</v>
       </c>
-      <c r="R15" s="14">
+      <c r="S15" s="14">
         <f t="shared" si="3"/>
         <v>-7.2407922601005037E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1387,28 +1424,28 @@
       <c r="F16" s="8">
         <v>3</v>
       </c>
-      <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="13">
+      <c r="K16" s="3"/>
+      <c r="L16" s="13">
         <f t="shared" si="0"/>
         <v>5.3595209643230426</v>
       </c>
-      <c r="L16" s="13">
+      <c r="M16" s="13">
         <f t="shared" si="1"/>
         <v>3.0000293047926361</v>
       </c>
-      <c r="Q16" s="14">
+      <c r="R16" s="14">
         <f t="shared" si="2"/>
         <v>-5.9520964323042769E-2</v>
       </c>
-      <c r="R16" s="14">
+      <c r="S16" s="14">
         <f t="shared" si="3"/>
         <v>-2.9304792636075661E-5</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1427,28 +1464,28 @@
       <c r="F17" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="13">
+      <c r="K17" s="3"/>
+      <c r="L17" s="13">
         <f t="shared" si="0"/>
         <v>4.9057563643916113</v>
       </c>
-      <c r="L17" s="13">
+      <c r="M17" s="13">
         <f t="shared" si="1"/>
         <v>4.6014510509501374</v>
       </c>
-      <c r="Q17" s="14">
+      <c r="R17" s="14">
         <f t="shared" si="2"/>
         <v>-5.7563643916109797E-3</v>
       </c>
-      <c r="R17" s="14">
+      <c r="S17" s="14">
         <f t="shared" si="3"/>
         <v>-1.4510509501377555E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -1467,28 +1504,28 @@
       <c r="F18" s="8">
         <v>3.8</v>
       </c>
-      <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="13">
+      <c r="K18" s="3"/>
+      <c r="L18" s="13">
         <f t="shared" si="0"/>
         <v>4.7595817556249012</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <f t="shared" si="1"/>
         <v>3.811795193441895</v>
       </c>
-      <c r="Q18" s="14">
+      <c r="R18" s="14">
         <f t="shared" si="2"/>
         <v>-5.9581755624900978E-2</v>
       </c>
-      <c r="R18" s="14">
+      <c r="S18" s="14">
         <f t="shared" si="3"/>
         <v>-1.1795193441895169E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1507,30 +1544,30 @@
       <c r="F19" s="8">
         <v>3.2</v>
       </c>
-      <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="13">
+      <c r="K19" s="3"/>
+      <c r="L19" s="13">
         <f t="shared" si="0"/>
         <v>4.8966576461535434</v>
       </c>
-      <c r="L19" s="13">
+      <c r="M19" s="13">
         <f t="shared" si="1"/>
         <v>3.2879822116723987</v>
       </c>
-      <c r="Q19" s="14">
+      <c r="R19" s="14">
         <f t="shared" si="2"/>
         <v>-9.6657646153543553E-2</v>
       </c>
-      <c r="R19" s="14">
+      <c r="S19" s="14">
         <f t="shared" si="3"/>
         <v>-8.7982211672398503E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B20" s="3">
         <v>765403</v>
@@ -1547,28 +1584,28 @@
       <c r="F20" s="8">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="13">
+      <c r="K20" s="3"/>
+      <c r="L20" s="13">
         <f t="shared" si="0"/>
         <v>3.5869992670527813</v>
       </c>
-      <c r="L20" s="13">
+      <c r="M20" s="13">
         <f t="shared" si="1"/>
         <v>2.2842868397432463</v>
       </c>
-      <c r="Q20" s="14">
+      <c r="R20" s="14">
         <f t="shared" si="2"/>
         <v>-8.6999267052781271E-2</v>
       </c>
-      <c r="R20" s="14">
+      <c r="S20" s="14">
         <f t="shared" si="3"/>
         <v>-8.4286839743246134E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1587,28 +1624,28 @@
       <c r="F21" s="8">
         <v>2.9</v>
       </c>
-      <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="13">
+      <c r="K21" s="3"/>
+      <c r="L21" s="13">
         <f t="shared" si="0"/>
         <v>4.4658700373701521</v>
       </c>
-      <c r="L21" s="13">
+      <c r="M21" s="13">
         <f t="shared" si="1"/>
         <v>2.8923667203386012</v>
       </c>
-      <c r="Q21" s="14">
+      <c r="R21" s="14">
         <f t="shared" si="2"/>
         <v>-6.5870037370151735E-2</v>
       </c>
-      <c r="R21" s="14">
+      <c r="S21" s="14">
         <f t="shared" si="3"/>
         <v>7.6332796613987064E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -1627,28 +1664,28 @@
       <c r="F22" s="8">
         <v>3.4</v>
       </c>
-      <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="13">
+      <c r="K22" s="3"/>
+      <c r="L22" s="13">
         <f t="shared" si="0"/>
         <v>5.1476005184048441</v>
       </c>
-      <c r="L22" s="13">
+      <c r="M22" s="13">
         <f t="shared" si="1"/>
         <v>3.4992326957594142</v>
       </c>
-      <c r="Q22" s="14">
+      <c r="R22" s="14">
         <f t="shared" si="2"/>
         <v>-4.7600518404844472E-2</v>
       </c>
-      <c r="R22" s="14">
+      <c r="S22" s="14">
         <f t="shared" si="3"/>
         <v>-9.9232695759414291E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -1667,28 +1704,28 @@
       <c r="F23" s="8">
         <v>2.7</v>
       </c>
-      <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="13">
+      <c r="K23" s="3"/>
+      <c r="L23" s="13">
         <f t="shared" si="0"/>
         <v>3.4243480961725798</v>
       </c>
-      <c r="L23" s="13">
+      <c r="M23" s="13">
         <f t="shared" si="1"/>
         <v>2.7147717807174825</v>
       </c>
-      <c r="Q23" s="14">
+      <c r="R23" s="14">
         <f t="shared" si="2"/>
         <v>-2.4348096172579936E-2</v>
       </c>
-      <c r="R23" s="14">
+      <c r="S23" s="14">
         <f t="shared" si="3"/>
         <v>-1.4771780717482308E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1707,28 +1744,28 @@
       <c r="F24" s="8">
         <v>3.4</v>
       </c>
-      <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="13">
+      <c r="K24" s="3"/>
+      <c r="L24" s="13">
         <f t="shared" si="0"/>
         <v>4.7529146951359662</v>
       </c>
-      <c r="L24" s="13">
+      <c r="M24" s="13">
         <f t="shared" si="1"/>
         <v>3.4803560247600478</v>
       </c>
-      <c r="Q24" s="14">
+      <c r="R24" s="14">
         <f t="shared" si="2"/>
         <v>-5.2914695135966028E-2</v>
       </c>
-      <c r="R24" s="14">
+      <c r="S24" s="14">
         <f t="shared" si="3"/>
         <v>-8.0356024760047884E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -1747,28 +1784,28 @@
       <c r="F25" s="8">
         <v>1.8</v>
       </c>
-      <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="13">
+      <c r="K25" s="3"/>
+      <c r="L25" s="13">
         <f t="shared" si="0"/>
         <v>2.7316832258439372</v>
       </c>
-      <c r="L25" s="13">
+      <c r="M25" s="13">
         <f t="shared" si="1"/>
         <v>1.8791761083028296</v>
       </c>
-      <c r="Q25" s="14">
+      <c r="R25" s="14">
         <f t="shared" si="2"/>
         <v>-3.1683225843937013E-2</v>
       </c>
-      <c r="R25" s="14">
+      <c r="S25" s="14">
         <f t="shared" si="3"/>
         <v>-7.9176108302829507E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -1787,28 +1824,28 @@
       <c r="F26" s="8">
         <v>3.9</v>
       </c>
-      <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="13">
+      <c r="K26" s="3"/>
+      <c r="L26" s="13">
         <f t="shared" si="0"/>
         <v>4.9441275676911776</v>
       </c>
-      <c r="L26" s="13">
+      <c r="M26" s="13">
         <f t="shared" si="1"/>
         <v>3.4364294415395373</v>
       </c>
-      <c r="Q26" s="14">
+      <c r="R26" s="14">
         <f t="shared" si="2"/>
         <v>-4.4127567691177205E-2</v>
       </c>
-      <c r="R26" s="14">
+      <c r="S26" s="14">
         <f t="shared" si="3"/>
         <v>0.46357055846046258</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -1827,30 +1864,30 @@
       <c r="F27" s="8">
         <v>2.9</v>
       </c>
-      <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="13">
+      <c r="K27" s="3"/>
+      <c r="L27" s="13">
         <f t="shared" si="0"/>
         <v>4.3138970996126638</v>
       </c>
-      <c r="L27" s="13">
+      <c r="M27" s="13">
         <f t="shared" si="1"/>
         <v>2.9911617003762747</v>
       </c>
-      <c r="Q27" s="14">
+      <c r="R27" s="14">
         <f t="shared" si="2"/>
         <v>-1.3897099612663943E-2</v>
       </c>
-      <c r="R27" s="14">
+      <c r="S27" s="14">
         <f t="shared" si="3"/>
         <v>-9.1161700376274801E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B28" s="3">
         <v>1860787</v>
@@ -1867,30 +1904,30 @@
       <c r="F28" s="8">
         <v>1.4</v>
       </c>
-      <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="13">
+      <c r="K28" s="3"/>
+      <c r="L28" s="13">
         <f t="shared" si="0"/>
         <v>2.0100634838914933</v>
       </c>
-      <c r="L28" s="13">
+      <c r="M28" s="13">
         <f t="shared" si="1"/>
         <v>1.4746448680047743</v>
       </c>
-      <c r="Q28" s="14">
+      <c r="R28" s="14">
         <f t="shared" si="2"/>
         <v>-1.0063483891493252E-2</v>
       </c>
-      <c r="R28" s="14">
+      <c r="S28" s="14">
         <f t="shared" si="3"/>
         <v>-7.4644868004774434E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B29" s="3">
         <v>542237</v>
@@ -1907,28 +1944,28 @@
       <c r="F29" s="8">
         <v>2.7</v>
       </c>
-      <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="13">
+      <c r="K29" s="3"/>
+      <c r="L29" s="13">
         <f t="shared" si="0"/>
         <v>4.0362424548675211</v>
       </c>
-      <c r="L29" s="13">
+      <c r="M29" s="13">
         <f t="shared" si="1"/>
         <v>2.7653959431023707</v>
       </c>
-      <c r="Q29" s="14">
+      <c r="R29" s="14">
         <f t="shared" si="2"/>
         <v>-3.624245486752109E-2</v>
       </c>
-      <c r="R29" s="14">
+      <c r="S29" s="14">
         <f t="shared" si="3"/>
         <v>-6.5395943102370513E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -1947,28 +1984,28 @@
       <c r="F30" s="8">
         <v>2.9</v>
       </c>
-      <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="13">
+      <c r="K30" s="3"/>
+      <c r="L30" s="13">
         <f t="shared" si="0"/>
         <v>4.0121713378476072</v>
       </c>
-      <c r="L30" s="13">
+      <c r="M30" s="13">
         <f t="shared" si="1"/>
         <v>2.9733304508927429</v>
       </c>
-      <c r="Q30" s="14">
+      <c r="R30" s="14">
         <f t="shared" si="2"/>
         <v>-1.2171337847607155E-2</v>
       </c>
-      <c r="R30" s="14">
+      <c r="S30" s="14">
         <f t="shared" si="3"/>
         <v>-7.3330450892743038E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1987,28 +2024,28 @@
       <c r="F31" s="8">
         <v>2.8</v>
       </c>
-      <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="13">
+      <c r="K31" s="3"/>
+      <c r="L31" s="13">
         <f t="shared" si="0"/>
         <v>4.1714495290060229</v>
       </c>
-      <c r="L31" s="13">
+      <c r="M31" s="13">
         <f t="shared" si="1"/>
         <v>2.8849667987851957</v>
       </c>
-      <c r="Q31" s="14">
+      <c r="R31" s="14">
         <f t="shared" si="2"/>
         <v>-7.1449529006023305E-2</v>
       </c>
-      <c r="R31" s="14">
+      <c r="S31" s="14">
         <f t="shared" si="3"/>
         <v>-8.4966798785195863E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -2027,28 +2064,28 @@
       <c r="F32" s="8">
         <v>2.8</v>
       </c>
-      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="13">
+      <c r="K32" s="3"/>
+      <c r="L32" s="13">
         <f t="shared" si="0"/>
         <v>4.9095308923051588</v>
       </c>
-      <c r="L32" s="13">
+      <c r="M32" s="13">
         <f t="shared" si="1"/>
         <v>2.8976246601479509</v>
       </c>
-      <c r="Q32" s="14">
+      <c r="R32" s="14">
         <f t="shared" si="2"/>
         <v>-9.5308923051584671E-3</v>
       </c>
-      <c r="R32" s="14">
+      <c r="S32" s="14">
         <f t="shared" si="3"/>
         <v>-9.7624660147951126E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -2067,28 +2104,28 @@
       <c r="F33" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="13">
+      <c r="K33" s="3"/>
+      <c r="L33" s="13">
         <f t="shared" si="0"/>
         <v>5.3501037060491408</v>
       </c>
-      <c r="L33" s="13">
+      <c r="M33" s="13">
         <f t="shared" si="1"/>
         <v>4.6110665259778809</v>
       </c>
-      <c r="Q33" s="14">
+      <c r="R33" s="14">
         <f t="shared" si="2"/>
         <v>-5.0103706049140939E-2</v>
       </c>
-      <c r="R33" s="14">
+      <c r="S33" s="14">
         <f t="shared" si="3"/>
         <v>-1.106652597788127E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>27</v>
       </c>
@@ -2107,28 +2144,28 @@
       <c r="F34" s="8">
         <v>3.2</v>
       </c>
-      <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="13">
+      <c r="K34" s="3"/>
+      <c r="L34" s="13">
         <f t="shared" si="0"/>
         <v>3.4924960079481453</v>
       </c>
-      <c r="L34" s="13">
+      <c r="M34" s="13">
         <f t="shared" si="1"/>
         <v>3.2731495724276067</v>
       </c>
-      <c r="Q34" s="14">
+      <c r="R34" s="14">
         <f t="shared" si="2"/>
         <v>-9.2496007948145387E-2</v>
       </c>
-      <c r="R34" s="14">
+      <c r="S34" s="14">
         <f t="shared" si="3"/>
         <v>-7.3149572427606557E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -2147,28 +2184,28 @@
       <c r="F35" s="8">
         <v>3.8</v>
       </c>
-      <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="13">
+      <c r="K35" s="3"/>
+      <c r="L35" s="13">
         <f t="shared" si="0"/>
         <v>5.3936516012724294</v>
       </c>
-      <c r="L35" s="13">
+      <c r="M35" s="13">
         <f t="shared" si="1"/>
         <v>3.8954504772318357</v>
       </c>
-      <c r="Q35" s="14">
+      <c r="R35" s="14">
         <f t="shared" si="2"/>
         <v>-9.3651601272429552E-2</v>
       </c>
-      <c r="R35" s="14">
+      <c r="S35" s="14">
         <f t="shared" si="3"/>
         <v>-9.5450477231835862E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -2187,28 +2224,28 @@
       <c r="F36" s="8">
         <v>3</v>
       </c>
-      <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="13">
+      <c r="K36" s="3"/>
+      <c r="L36" s="13">
         <f t="shared" si="0"/>
         <v>4.3456356296797223</v>
       </c>
-      <c r="L36" s="13">
+      <c r="M36" s="13">
         <f t="shared" si="1"/>
         <v>3.0853101065304167</v>
       </c>
-      <c r="Q36" s="14">
+      <c r="R36" s="14">
         <f t="shared" si="2"/>
         <v>-4.5635629679722456E-2</v>
       </c>
-      <c r="R36" s="14">
+      <c r="S36" s="14">
         <f t="shared" si="3"/>
         <v>-8.5310106530416707E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>30</v>
       </c>
@@ -2227,28 +2264,28 @@
       <c r="F37" s="8">
         <v>3.6</v>
       </c>
-      <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="13">
+      <c r="K37" s="3"/>
+      <c r="L37" s="13">
         <f t="shared" si="0"/>
         <v>4.8693723580882606</v>
       </c>
-      <c r="L37" s="13">
+      <c r="M37" s="13">
         <f t="shared" si="1"/>
         <v>3.60499272646849</v>
       </c>
-      <c r="Q37" s="14">
+      <c r="R37" s="14">
         <f t="shared" si="2"/>
         <v>-6.937235808826081E-2</v>
       </c>
-      <c r="R37" s="14">
+      <c r="S37" s="14">
         <f t="shared" si="3"/>
         <v>-4.9927264684899164E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -2267,28 +2304,28 @@
       <c r="F38" s="8">
         <v>3.6</v>
       </c>
-      <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="13">
+      <c r="K38" s="3"/>
+      <c r="L38" s="13">
         <f t="shared" si="0"/>
         <v>5.4692915569111324</v>
       </c>
-      <c r="L38" s="13">
+      <c r="M38" s="13">
         <f t="shared" si="1"/>
         <v>3.6502988026005676</v>
       </c>
-      <c r="Q38" s="14">
+      <c r="R38" s="14">
         <f t="shared" si="2"/>
         <v>-6.9291556911132091E-2</v>
       </c>
-      <c r="R38" s="14">
+      <c r="S38" s="14">
         <f t="shared" si="3"/>
         <v>-5.0298802600567516E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>32</v>
       </c>
@@ -2307,28 +2344,28 @@
       <c r="F39" s="8">
         <v>3.4</v>
       </c>
-      <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="13">
+      <c r="K39" s="3"/>
+      <c r="L39" s="13">
         <f t="shared" si="0"/>
         <v>4.9997575984882667</v>
       </c>
-      <c r="L39" s="13">
+      <c r="M39" s="13">
         <f t="shared" si="1"/>
         <v>3.4378394620071591</v>
       </c>
-      <c r="Q39" s="14">
+      <c r="R39" s="14">
         <f t="shared" si="2"/>
         <v>-9.9757598488266375E-2</v>
       </c>
-      <c r="R39" s="14">
+      <c r="S39" s="14">
         <f t="shared" si="3"/>
         <v>-3.7839462007159153E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -2347,28 +2384,28 @@
       <c r="F40" s="8">
         <v>3.5</v>
       </c>
-      <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="13">
+      <c r="K40" s="3"/>
+      <c r="L40" s="13">
         <f t="shared" si="0"/>
         <v>5.5541508700982112</v>
       </c>
-      <c r="L40" s="13">
+      <c r="M40" s="13">
         <f t="shared" si="1"/>
         <v>3.5854371057615118</v>
       </c>
-      <c r="Q40" s="14">
+      <c r="R40" s="14">
         <f t="shared" si="2"/>
         <v>-5.4150870098211179E-2</v>
       </c>
-      <c r="R40" s="14">
+      <c r="S40" s="14">
         <f t="shared" si="3"/>
         <v>-8.5437105761511756E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>34</v>
       </c>
@@ -2387,30 +2424,30 @@
       <c r="F41" s="8">
         <v>4.2</v>
       </c>
-      <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="13">
+      <c r="K41" s="3"/>
+      <c r="L41" s="13">
         <f t="shared" si="0"/>
         <v>6.0157230317545167</v>
       </c>
-      <c r="L41" s="13">
+      <c r="M41" s="13">
         <f t="shared" si="1"/>
         <v>4.2621431189934418</v>
       </c>
-      <c r="Q41" s="14">
+      <c r="R41" s="14">
         <f t="shared" si="2"/>
         <v>-1.5723031754516725E-2</v>
       </c>
-      <c r="R41" s="14">
+      <c r="S41" s="14">
         <f t="shared" si="3"/>
         <v>-6.2143118993441604E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B42" s="3">
         <v>837928</v>
@@ -2427,28 +2464,28 @@
       <c r="F42" s="8">
         <v>2.4</v>
       </c>
-      <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="13">
+      <c r="K42" s="3"/>
+      <c r="L42" s="13">
         <f t="shared" si="0"/>
         <v>3.8759893451465999</v>
       </c>
-      <c r="L42" s="13">
+      <c r="M42" s="13">
         <f t="shared" si="1"/>
         <v>2.4477043373655016</v>
       </c>
-      <c r="Q42" s="14">
+      <c r="R42" s="14">
         <f t="shared" si="2"/>
         <v>-7.5989345146600051E-2</v>
       </c>
-      <c r="R42" s="14">
+      <c r="S42" s="14">
         <f t="shared" si="3"/>
         <v>-4.7704337365501726E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>35</v>
       </c>
@@ -2467,28 +2504,28 @@
       <c r="F43" s="8">
         <v>2.8</v>
       </c>
-      <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="13">
+      <c r="K43" s="3"/>
+      <c r="L43" s="13">
         <f t="shared" si="0"/>
         <v>4.0775402330508079</v>
       </c>
-      <c r="L43" s="13">
+      <c r="M43" s="13">
         <f t="shared" si="1"/>
         <v>3.0107583677765852</v>
       </c>
-      <c r="Q43" s="14">
+      <c r="R43" s="14">
         <f t="shared" si="2"/>
         <v>-7.7540233050807927E-2</v>
       </c>
-      <c r="R43" s="14">
+      <c r="S43" s="14">
         <f t="shared" si="3"/>
         <v>-0.21075836777658541</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -2507,28 +2544,28 @@
       <c r="F44" s="8">
         <v>3.1</v>
       </c>
-      <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="13">
+      <c r="K44" s="3"/>
+      <c r="L44" s="13">
         <f t="shared" si="0"/>
         <v>4.9168568811360327</v>
       </c>
-      <c r="L44" s="13">
+      <c r="M44" s="13">
         <f t="shared" si="1"/>
         <v>3.1779540862877256</v>
       </c>
-      <c r="Q44" s="14">
+      <c r="R44" s="14">
         <f t="shared" si="2"/>
         <v>-1.6856881136032342E-2</v>
       </c>
-      <c r="R44" s="14">
+      <c r="S44" s="14">
         <f t="shared" si="3"/>
         <v>-7.7954086287725488E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -2547,28 +2584,28 @@
       <c r="F45" s="8">
         <v>2.9</v>
       </c>
-      <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="13">
+      <c r="K45" s="3"/>
+      <c r="L45" s="13">
         <f t="shared" si="0"/>
         <v>4.5233483123369655</v>
       </c>
-      <c r="L45" s="13">
+      <c r="M45" s="13">
         <f t="shared" si="1"/>
         <v>2.9459933925541715</v>
       </c>
-      <c r="Q45" s="14">
+      <c r="R45" s="14">
         <f t="shared" si="2"/>
         <v>-2.3348312336965549E-2</v>
       </c>
-      <c r="R45" s="14">
+      <c r="S45" s="14">
         <f t="shared" si="3"/>
         <v>-4.5993392554171564E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -2587,30 +2624,30 @@
       <c r="F46" s="8">
         <v>3.9</v>
       </c>
-      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
-      <c r="K46" s="13">
+      <c r="K46" s="3"/>
+      <c r="L46" s="13">
         <f t="shared" si="0"/>
         <v>4.7975631710202311</v>
       </c>
-      <c r="L46" s="13">
+      <c r="M46" s="13">
         <f t="shared" si="1"/>
         <v>3.9975577837785665</v>
       </c>
-      <c r="Q46" s="14">
+      <c r="R46" s="14">
         <f t="shared" si="2"/>
         <v>-9.7563171020230932E-2</v>
       </c>
-      <c r="R46" s="14">
+      <c r="S46" s="14">
         <f t="shared" si="3"/>
         <v>-9.7557783778566609E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B47" s="3">
         <v>633725</v>
@@ -2627,28 +2664,28 @@
       <c r="F47" s="8">
         <v>2.7</v>
       </c>
-      <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="13">
+      <c r="K47" s="3"/>
+      <c r="L47" s="13">
         <f t="shared" si="0"/>
         <v>4.1966152510947179</v>
       </c>
-      <c r="L47" s="13">
+      <c r="M47" s="13">
         <f t="shared" si="1"/>
         <v>2.7041697897352952</v>
       </c>
-      <c r="Q47" s="14">
+      <c r="R47" s="14">
         <f t="shared" si="2"/>
         <v>-9.6615251094718246E-2</v>
       </c>
-      <c r="R47" s="14">
+      <c r="S47" s="14">
         <f t="shared" si="3"/>
         <v>-4.1697897352950264E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -2667,28 +2704,28 @@
       <c r="F48" s="8">
         <v>3.1</v>
       </c>
-      <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="13">
+      <c r="K48" s="3"/>
+      <c r="L48" s="13">
         <f t="shared" si="0"/>
         <v>4.6070352549020077</v>
       </c>
-      <c r="L48" s="13">
+      <c r="M48" s="13">
         <f t="shared" si="1"/>
         <v>3.126455651113115</v>
       </c>
-      <c r="Q48" s="14">
+      <c r="R48" s="14">
         <f t="shared" si="2"/>
         <v>-7.0352549020080701E-3</v>
       </c>
-      <c r="R48" s="14">
+      <c r="S48" s="14">
         <f t="shared" si="3"/>
         <v>-2.6455651113114875E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>40</v>
       </c>
@@ -2707,28 +2744,28 @@
       <c r="F49" s="8">
         <v>3.7</v>
       </c>
-      <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="13">
+      <c r="K49" s="3"/>
+      <c r="L49" s="13">
         <f t="shared" si="0"/>
         <v>5.5154757531227041</v>
       </c>
-      <c r="L49" s="13">
+      <c r="M49" s="13">
         <f t="shared" si="1"/>
         <v>3.7446271124173403</v>
       </c>
-      <c r="Q49" s="14">
+      <c r="R49" s="14">
         <f t="shared" si="2"/>
         <v>-1.5475753122704106E-2</v>
       </c>
-      <c r="R49" s="14">
+      <c r="S49" s="14">
         <f t="shared" si="3"/>
         <v>-4.4627112417340076E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>41</v>
       </c>
@@ -2747,28 +2784,28 @@
       <c r="F50" s="8">
         <v>3.6</v>
       </c>
-      <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
-      <c r="K50" s="13">
+      <c r="K50" s="3"/>
+      <c r="L50" s="13">
         <f t="shared" si="0"/>
         <v>3.6222486615110054</v>
       </c>
-      <c r="L50" s="13">
+      <c r="M50" s="13">
         <f t="shared" si="1"/>
         <v>3.6157049375371799</v>
       </c>
-      <c r="Q50" s="14">
+      <c r="R50" s="14">
         <f t="shared" si="2"/>
         <v>-2.2248661511005352E-2</v>
       </c>
-      <c r="R50" s="14">
+      <c r="S50" s="14">
         <f t="shared" si="3"/>
         <v>-1.5704937537179831E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>42</v>
       </c>
@@ -2787,30 +2824,30 @@
       <c r="F51" s="8">
         <v>3.8</v>
       </c>
-      <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
-      <c r="K51" s="13">
+      <c r="K51" s="3"/>
+      <c r="L51" s="13">
         <f t="shared" si="0"/>
         <v>3.052719509931316</v>
       </c>
-      <c r="L51" s="13">
+      <c r="M51" s="13">
         <f t="shared" si="1"/>
         <v>3.823556710599592</v>
       </c>
-      <c r="Q51" s="14">
+      <c r="R51" s="14">
         <f t="shared" si="2"/>
         <v>-5.2719509931316022E-2</v>
       </c>
-      <c r="R51" s="14">
+      <c r="S51" s="14">
         <f t="shared" si="3"/>
         <v>-2.355671059959219E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B52" s="3">
         <v>67173</v>
@@ -2818,14 +2855,17 @@
       <c r="D52" s="3">
         <v>1832</v>
       </c>
-      <c r="G52" s="3"/>
+      <c r="G52" t="s">
+        <v>41</v>
+      </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
-      <c r="Q52" s="14"/>
+      <c r="K52" s="3"/>
       <c r="R52" s="14"/>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="S52" s="14"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>43</v>
       </c>
@@ -2844,28 +2884,28 @@
       <c r="F53" s="8">
         <v>3.8</v>
       </c>
-      <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
-      <c r="K53" s="13">
+      <c r="K53" s="3"/>
+      <c r="L53" s="13">
         <f t="shared" si="0"/>
         <v>4.9549661934582474</v>
       </c>
-      <c r="L53" s="13">
+      <c r="M53" s="13">
         <f t="shared" si="1"/>
         <v>3.8692236456469771</v>
       </c>
-      <c r="Q53" s="14">
+      <c r="R53" s="14">
         <f t="shared" si="2"/>
         <v>-5.4966193458247048E-2</v>
       </c>
-      <c r="R53" s="14">
+      <c r="S53" s="14">
         <f t="shared" si="3"/>
         <v>-6.922364564697725E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>44</v>
       </c>
@@ -2884,28 +2924,28 @@
       <c r="F54" s="8">
         <v>3</v>
       </c>
-      <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
-      <c r="K54" s="13">
+      <c r="K54" s="3"/>
+      <c r="L54" s="13">
         <f t="shared" si="0"/>
         <v>4.9911011375067709</v>
       </c>
-      <c r="L54" s="13">
+      <c r="M54" s="13">
         <f t="shared" si="1"/>
         <v>3.0444450074950407</v>
       </c>
-      <c r="Q54" s="14">
+      <c r="R54" s="14">
         <f t="shared" si="2"/>
         <v>-9.1101137506770513E-2</v>
       </c>
-      <c r="R54" s="14">
+      <c r="S54" s="14">
         <f t="shared" si="3"/>
         <v>-4.4445007495040656E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>45</v>
       </c>
@@ -2924,30 +2964,30 @@
       <c r="F55" s="8">
         <v>3.6</v>
       </c>
-      <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
-      <c r="K55" s="13">
+      <c r="K55" s="3"/>
+      <c r="L55" s="13">
         <f t="shared" si="0"/>
         <v>5.3234364743284468</v>
       </c>
-      <c r="L55" s="13">
+      <c r="M55" s="13">
         <f t="shared" si="1"/>
         <v>3.6442311405145893</v>
       </c>
-      <c r="Q55" s="14">
+      <c r="R55" s="14">
         <f t="shared" si="2"/>
         <v>-2.3436474328446977E-2</v>
       </c>
-      <c r="R55" s="14">
+      <c r="S55" s="14">
         <f t="shared" si="3"/>
         <v>-4.4231140514589207E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B56" s="3">
         <v>603174</v>
@@ -2964,28 +3004,28 @@
       <c r="F56" s="8">
         <v>2.1</v>
       </c>
-      <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
-      <c r="K56" s="13">
+      <c r="K56" s="3"/>
+      <c r="L56" s="13">
         <f t="shared" si="0"/>
         <v>2.9033081664660614</v>
       </c>
-      <c r="L56" s="13">
+      <c r="M56" s="13">
         <f t="shared" si="1"/>
         <v>2.1764863870127029</v>
       </c>
-      <c r="Q56" s="14">
+      <c r="R56" s="14">
         <f t="shared" si="2"/>
         <v>-3.3081664660614685E-3</v>
       </c>
-      <c r="R56" s="14">
+      <c r="S56" s="14">
         <f t="shared" si="3"/>
         <v>-7.6486387012702828E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>46</v>
       </c>
@@ -3004,28 +3044,28 @@
       <c r="F57" s="8">
         <v>2.5</v>
       </c>
-      <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
-      <c r="K57" s="13">
+      <c r="K57" s="3"/>
+      <c r="L57" s="13">
         <f t="shared" si="0"/>
         <v>3.2822561943666493</v>
       </c>
-      <c r="L57" s="13">
+      <c r="M57" s="13">
         <f t="shared" si="1"/>
         <v>2.53564021023305</v>
       </c>
-      <c r="Q57" s="14">
+      <c r="R57" s="14">
         <f t="shared" si="2"/>
         <v>-8.2256194366649105E-2</v>
       </c>
-      <c r="R57" s="14">
+      <c r="S57" s="14">
         <f t="shared" si="3"/>
         <v>-3.5640210233049974E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>47</v>
       </c>
@@ -3044,28 +3084,29 @@
       <c r="F58" s="15">
         <v>2.6</v>
       </c>
-      <c r="G58" s="3"/>
+      <c r="G58" s="15"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
-      <c r="K58" s="13">
+      <c r="K58" s="3"/>
+      <c r="L58" s="13">
         <f t="shared" si="0"/>
         <v>4.8444807379651236</v>
       </c>
-      <c r="L58" s="13">
+      <c r="M58" s="13">
         <f t="shared" si="1"/>
         <v>2.6457765293370081</v>
       </c>
-      <c r="Q58" s="14">
+      <c r="R58" s="14">
         <f t="shared" si="2"/>
         <v>-4.4480737965123751E-2</v>
       </c>
-      <c r="R58" s="14">
+      <c r="S58" s="14">
         <f t="shared" si="3"/>
         <v>-4.5776529337008043E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>48</v>
       </c>
@@ -3084,28 +3125,28 @@
       <c r="F59" s="8">
         <v>3.3</v>
       </c>
-      <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
-      <c r="K59" s="13">
+      <c r="K59" s="3"/>
+      <c r="L59" s="13">
         <f t="shared" si="0"/>
         <v>4.9449516954584949</v>
       </c>
-      <c r="L59" s="13">
+      <c r="M59" s="13">
         <f t="shared" si="1"/>
         <v>3.3960825976747442</v>
       </c>
-      <c r="Q59" s="14">
+      <c r="R59" s="14">
         <f t="shared" si="2"/>
         <v>-4.4951695458494534E-2</v>
       </c>
-      <c r="R59" s="14">
+      <c r="S59" s="14">
         <f t="shared" si="3"/>
         <v>-9.6082597674744363E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>49</v>
       </c>
@@ -3124,28 +3165,28 @@
       <c r="F60" s="8">
         <v>3.2</v>
       </c>
-      <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
-      <c r="K60" s="13">
+      <c r="K60" s="3"/>
+      <c r="L60" s="13">
         <f t="shared" si="0"/>
         <v>4.8450687097166485</v>
       </c>
-      <c r="L60" s="13">
+      <c r="M60" s="13">
         <f t="shared" si="1"/>
         <v>3.2361060440228631</v>
       </c>
-      <c r="Q60" s="14">
+      <c r="R60" s="14">
         <f t="shared" si="2"/>
         <v>-4.5068709716648669E-2</v>
       </c>
-      <c r="R60" s="14">
+      <c r="S60" s="14">
         <f t="shared" si="3"/>
         <v>-3.6106044022862882E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -3164,28 +3205,28 @@
       <c r="F61" s="8">
         <v>4.2</v>
       </c>
-      <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
-      <c r="K61" s="13">
+      <c r="K61" s="3"/>
+      <c r="L61" s="13">
         <f t="shared" si="0"/>
         <v>5.5157245436064253</v>
       </c>
-      <c r="L61" s="13">
+      <c r="M61" s="13">
         <f t="shared" si="1"/>
         <v>4.2681406529298531</v>
       </c>
-      <c r="Q61" s="14">
+      <c r="R61" s="14">
         <f t="shared" si="2"/>
         <v>-1.5724543606425279E-2</v>
       </c>
-      <c r="R61" s="14">
+      <c r="S61" s="14">
         <f t="shared" si="3"/>
         <v>-6.8140652929852941E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>51</v>
       </c>
@@ -3204,28 +3245,28 @@
       <c r="F62" s="8">
         <v>2.5</v>
       </c>
-      <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
-      <c r="K62" s="13">
+      <c r="K62" s="3"/>
+      <c r="L62" s="13">
         <f t="shared" si="0"/>
         <v>4.2671230335411101</v>
       </c>
-      <c r="L62" s="13">
+      <c r="M62" s="13">
         <f t="shared" si="1"/>
         <v>2.5091829919857522</v>
       </c>
-      <c r="Q62" s="14">
+      <c r="R62" s="14">
         <f t="shared" si="2"/>
         <v>-6.7123033541109933E-2</v>
       </c>
-      <c r="R62" s="14">
+      <c r="S62" s="14">
         <f t="shared" si="3"/>
         <v>-9.1829919857522313E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>52</v>
       </c>
@@ -3244,28 +3285,28 @@
       <c r="F63" s="8">
         <v>3.7</v>
       </c>
-      <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
-      <c r="K63" s="13">
+      <c r="K63" s="3"/>
+      <c r="L63" s="13">
         <f t="shared" si="0"/>
         <v>5.1347197106690778</v>
       </c>
-      <c r="L63" s="13">
+      <c r="M63" s="13">
         <f t="shared" si="1"/>
         <v>3.7781796262808918</v>
       </c>
-      <c r="Q63" s="14">
+      <c r="R63" s="14">
         <f t="shared" si="2"/>
         <v>-3.4719710669078196E-2</v>
       </c>
-      <c r="R63" s="14">
+      <c r="S63" s="14">
         <f t="shared" si="3"/>
         <v>-7.817962628089159E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>53</v>
       </c>
@@ -3284,28 +3325,28 @@
       <c r="F64" s="8">
         <v>3.1</v>
       </c>
-      <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
-      <c r="K64" s="13">
+      <c r="K64" s="3"/>
+      <c r="L64" s="13">
         <f t="shared" si="0"/>
         <v>4.952627326858682</v>
       </c>
-      <c r="L64" s="13">
+      <c r="M64" s="13">
         <f t="shared" si="1"/>
         <v>3.1130444177058223</v>
       </c>
-      <c r="Q64" s="14">
+      <c r="R64" s="14">
         <f t="shared" si="2"/>
         <v>-5.2627326858681656E-2</v>
       </c>
-      <c r="R64" s="14">
+      <c r="S64" s="14">
         <f t="shared" si="3"/>
         <v>-1.3044417705822209E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>54</v>
       </c>
@@ -3324,28 +3365,28 @@
       <c r="F65" s="8">
         <v>3</v>
       </c>
-      <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
-      <c r="K65" s="13">
+      <c r="K65" s="3"/>
+      <c r="L65" s="13">
         <f t="shared" si="0"/>
         <v>4.8140370115988853</v>
       </c>
-      <c r="L65" s="13">
+      <c r="M65" s="13">
         <f t="shared" si="1"/>
         <v>3.0955137880055239</v>
       </c>
-      <c r="Q65" s="14">
+      <c r="R65" s="14">
         <f t="shared" si="2"/>
         <v>-1.4037011598885485E-2</v>
       </c>
-      <c r="R65" s="14">
+      <c r="S65" s="14">
         <f t="shared" si="3"/>
         <v>-9.5513788005523903E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>55</v>
       </c>
@@ -3364,30 +3405,30 @@
       <c r="F66" s="8">
         <v>2.6</v>
       </c>
-      <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
-      <c r="K66" s="13">
+      <c r="K66" s="3"/>
+      <c r="L66" s="13">
         <f t="shared" si="0"/>
         <v>4.9934272791072978</v>
       </c>
-      <c r="L66" s="13">
+      <c r="M66" s="13">
         <f t="shared" si="1"/>
         <v>2.6376976120895312</v>
       </c>
-      <c r="Q66" s="14">
+      <c r="R66" s="14">
         <f t="shared" si="2"/>
         <v>-9.3427279107297423E-2</v>
       </c>
-      <c r="R66" s="14">
+      <c r="S66" s="14">
         <f t="shared" si="3"/>
         <v>-3.7697612089531152E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B67" s="3">
         <v>1875855</v>
@@ -3404,28 +3445,28 @@
       <c r="F67" s="8">
         <v>3</v>
       </c>
-      <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
-      <c r="K67" s="13">
+      <c r="K67" s="3"/>
+      <c r="L67" s="13">
         <f t="shared" si="0"/>
         <v>4.4989084977250373</v>
       </c>
-      <c r="L67" s="13">
+      <c r="M67" s="13">
         <f t="shared" si="1"/>
         <v>3.0265665523188092</v>
       </c>
-      <c r="Q67" s="14">
+      <c r="R67" s="14">
         <f t="shared" si="2"/>
         <v>-9.8908497725036959E-2</v>
       </c>
-      <c r="R67" s="14">
+      <c r="S67" s="14">
         <f t="shared" si="3"/>
         <v>-2.6566552318809222E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>56</v>
       </c>
@@ -3444,28 +3485,28 @@
       <c r="F68" s="8">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
-      <c r="K68" s="13">
+      <c r="K68" s="3"/>
+      <c r="L68" s="13">
         <f t="shared" si="0"/>
         <v>3.0673593752552728</v>
       </c>
-      <c r="L68" s="13">
+      <c r="M68" s="13">
         <f t="shared" si="1"/>
         <v>2.2300642062441796</v>
       </c>
-      <c r="Q68" s="14">
+      <c r="R68" s="14">
         <f t="shared" si="2"/>
         <v>-6.7359375255272802E-2</v>
       </c>
-      <c r="R68" s="14">
+      <c r="S68" s="14">
         <f t="shared" si="3"/>
         <v>-3.0064206244179381E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>57</v>
       </c>
@@ -3484,28 +3525,28 @@
       <c r="F69" s="8">
         <v>2.9</v>
       </c>
-      <c r="G69" s="3"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
-      <c r="K69" s="13">
-        <f t="shared" ref="K69:K70" si="4">100*C69/B69</f>
+      <c r="K69" s="3"/>
+      <c r="L69" s="13">
+        <f t="shared" ref="L69:L70" si="4">100*C69/B69</f>
         <v>4.0738820244408096</v>
       </c>
-      <c r="L69" s="13">
-        <f t="shared" ref="L69:L70" si="5">D69/B69*100</f>
+      <c r="M69" s="13">
+        <f t="shared" ref="M69:M70" si="5">D69/B69*100</f>
         <v>2.9684400911779507</v>
       </c>
-      <c r="Q69" s="14">
-        <f t="shared" ref="Q69:Q70" si="6">E69-K69</f>
+      <c r="R69" s="14">
+        <f t="shared" ref="R69:R70" si="6">E69-L69</f>
         <v>-7.3882024440809602E-2</v>
       </c>
-      <c r="R69" s="14">
-        <f t="shared" ref="R69:R70" si="7">F69-L69</f>
+      <c r="S69" s="14">
+        <f t="shared" ref="S69:S70" si="7">F69-M69</f>
         <v>-6.8440091177950801E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>58</v>
       </c>
@@ -3524,56 +3565,57 @@
       <c r="F70" s="11">
         <v>3.26</v>
       </c>
-      <c r="G70" s="3"/>
-      <c r="H70" s="6">
+      <c r="G70" s="11"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="6">
         <f>SUM(B3:B69)</f>
         <v>85811455</v>
       </c>
-      <c r="I70" s="6">
+      <c r="J70" s="6">
         <f>SUM(C3:C69)</f>
         <v>4004335</v>
       </c>
-      <c r="J70" s="6">
+      <c r="K70" s="6">
         <f>SUM(D3:D69)</f>
         <v>2797031</v>
       </c>
-      <c r="K70" s="13">
+      <c r="L70" s="13">
         <f t="shared" si="4"/>
         <v>4.6512360449056862</v>
       </c>
-      <c r="L70" s="13">
+      <c r="M70" s="13">
         <f t="shared" si="5"/>
         <v>3.2450907895051944</v>
       </c>
-      <c r="N70" s="6">
-        <f>B70-H70</f>
+      <c r="O70" s="6">
+        <f>B70-I70</f>
         <v>-50</v>
       </c>
-      <c r="O70" s="6">
-        <f>C70-I70</f>
+      <c r="P70" s="6">
+        <f>C70-J70</f>
         <v>-13044</v>
       </c>
-      <c r="P70" s="6">
-        <f>D70-J70</f>
+      <c r="Q70" s="6">
+        <f>D70-K70</f>
         <v>-12373</v>
       </c>
-      <c r="Q70" s="14">
+      <c r="R70" s="14">
         <f t="shared" si="6"/>
         <v>1.8763955094313722E-2</v>
       </c>
-      <c r="R70" s="14">
+      <c r="S70" s="14">
         <f t="shared" si="7"/>
         <v>1.4909210494805425E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="G71" s="3"/>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" t="s">
+      <c r="K71" s="3"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="16" t="s">
         <v>59</v>
       </c>
       <c r="B72" s="3">
@@ -3591,13 +3633,13 @@
       <c r="F72" s="8">
         <v>2.1</v>
       </c>
-      <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" t="s">
+      <c r="K72" s="3"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="16" t="s">
         <v>60</v>
       </c>
       <c r="B73" s="3">
@@ -3615,13 +3657,13 @@
       <c r="F73" s="8">
         <v>2.1</v>
       </c>
-      <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" t="s">
+      <c r="K73" s="3"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="16" t="s">
         <v>61</v>
       </c>
       <c r="B74" s="3">
@@ -3639,14 +3681,14 @@
       <c r="F74" s="8">
         <v>2.4</v>
       </c>
-      <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" t="s">
-        <v>82</v>
+      <c r="K74" s="3"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="16" t="s">
+        <v>80</v>
       </c>
       <c r="B75" s="3">
         <v>74000</v>
@@ -3663,13 +3705,13 @@
       <c r="F75" s="8">
         <v>0.6</v>
       </c>
-      <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" t="s">
+      <c r="K75" s="3"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="16" t="s">
         <v>62</v>
       </c>
       <c r="B76" s="3">
@@ -3687,85 +3729,88 @@
       <c r="F76" s="8">
         <v>2</v>
       </c>
-      <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" t="s">
-        <v>83</v>
+      <c r="K76" s="3"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="B77" s="3">
         <v>685945</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G77" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="G77" s="9"/>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" t="s">
-        <v>84</v>
+      <c r="K77" s="3"/>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="B78" s="3">
         <v>1109542</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G78" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="G78" s="9"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" t="s">
+      <c r="K78" s="3"/>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="16" t="s">
         <v>63</v>
       </c>
       <c r="B79" s="3">
         <v>320075</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G79" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="G79" s="9"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" t="s">
+      <c r="K79" s="3"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="16" t="s">
         <v>64</v>
       </c>
       <c r="B80" s="3">
@@ -3783,37 +3828,38 @@
       <c r="F80" s="8">
         <v>0.6</v>
       </c>
-      <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" t="s">
+      <c r="K80" s="3"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="16" t="s">
         <v>65</v>
       </c>
       <c r="B81" s="3">
         <v>808000</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G81" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="G81" s="9"/>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" t="s">
+      <c r="K81" s="3"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="16" t="s">
         <v>66</v>
       </c>
       <c r="B82" s="3">
@@ -3831,13 +3877,13 @@
       <c r="F82" s="8">
         <v>1.5</v>
       </c>
-      <c r="G82" s="3"/>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" t="s">
+      <c r="K82" s="3"/>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="16" t="s">
         <v>67</v>
       </c>
       <c r="B83" s="3">
@@ -3855,57 +3901,58 @@
       <c r="F83" s="8">
         <v>1.7</v>
       </c>
-      <c r="G83" s="3"/>
-      <c r="H83" s="6">
+      <c r="H83" s="3"/>
+      <c r="I83" s="6">
         <f>SUM(B72:B82)</f>
         <v>5307109</v>
       </c>
-      <c r="I83" s="6">
+      <c r="J83" s="6">
         <f>SUM(C72:C82)</f>
         <v>52572</v>
       </c>
-      <c r="J83" s="6">
+      <c r="K83" s="6">
         <f>SUM(D72:D82)</f>
         <v>41780</v>
       </c>
-      <c r="K83" s="13">
-        <f t="shared" ref="K83" si="8">100*C83/B83</f>
+      <c r="L83" s="13">
+        <f t="shared" ref="L83" si="8">100*C83/B83</f>
         <v>0.99059582156688319</v>
       </c>
-      <c r="L83" s="13">
-        <f t="shared" ref="L83" si="9">D83/B83*100</f>
+      <c r="M83" s="13">
+        <f t="shared" ref="M83" si="9">D83/B83*100</f>
         <v>0.78724593747744775</v>
       </c>
-      <c r="N83" s="6">
-        <f>B83-H83</f>
+      <c r="O83" s="6">
+        <f>B83-I83</f>
         <v>0</v>
       </c>
-      <c r="O83" s="6">
-        <f>C83-I83</f>
+      <c r="P83" s="6">
+        <f>C83-J83</f>
         <v>0</v>
       </c>
-      <c r="P83" s="6">
-        <f>D83-J83</f>
+      <c r="Q83" s="6">
+        <f>D83-K83</f>
         <v>0</v>
       </c>
-      <c r="Q83" s="14">
-        <f t="shared" ref="Q83" si="10">E83-K83</f>
+      <c r="R83" s="14">
+        <f t="shared" ref="R83" si="10">E83-L83</f>
         <v>1.2094041784331169</v>
       </c>
-      <c r="R83" s="14">
-        <f t="shared" ref="R83" si="11">F83-L83</f>
+      <c r="S83" s="14">
+        <f t="shared" ref="S83" si="11">F83-M83</f>
         <v>0.9127540625225522</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="G84" s="3"/>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="16"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" t="s">
-        <v>68</v>
+      <c r="K84" s="3"/>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="B85" s="3">
         <v>23194</v>
@@ -3922,13 +3969,13 @@
       <c r="F85" s="8">
         <v>4.2</v>
       </c>
-      <c r="G85" s="3"/>
-      <c r="I85" s="3"/>
+      <c r="H85" s="3"/>
       <c r="J85" s="3"/>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" t="s">
-        <v>69</v>
+      <c r="K85" s="3"/>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="16" t="s">
+        <v>106</v>
       </c>
       <c r="B86" s="3">
         <v>28622</v>
@@ -3945,18 +3992,19 @@
       <c r="F86" s="8">
         <v>3</v>
       </c>
-      <c r="G86" s="3"/>
-      <c r="I86" s="3"/>
+      <c r="H86" s="3"/>
       <c r="J86" s="3"/>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="G87" s="3"/>
-      <c r="I87" s="3"/>
+      <c r="K86" s="3"/>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="16"/>
+      <c r="H87" s="3"/>
       <c r="J87" s="3"/>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" t="s">
-        <v>92</v>
+      <c r="K87" s="3"/>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="16" t="s">
+        <v>107</v>
       </c>
       <c r="B88" s="3">
         <f>SUM(B85:B86)</f>
@@ -3970,50 +4018,51 @@
         <f>SUM(D85:D86)</f>
         <v>1849</v>
       </c>
-      <c r="G88" s="3"/>
-      <c r="H88" s="6">
+      <c r="H88" s="3"/>
+      <c r="I88" s="6">
         <f>B88</f>
         <v>51816</v>
       </c>
-      <c r="I88" s="6">
+      <c r="J88" s="6">
         <f>C88</f>
         <v>2454</v>
       </c>
-      <c r="J88" s="6">
+      <c r="K88" s="6">
         <f>D88</f>
         <v>1849</v>
       </c>
-      <c r="K88" s="13">
-        <f t="shared" ref="K88" si="12">100*C88/B88</f>
+      <c r="L88" s="13">
+        <f t="shared" ref="L88" si="12">100*C88/B88</f>
         <v>4.7359888837424737</v>
       </c>
-      <c r="L88" s="13">
-        <f t="shared" ref="L88" si="13">D88/B88*100</f>
+      <c r="M88" s="13">
+        <f t="shared" ref="M88" si="13">D88/B88*100</f>
         <v>3.5683958622819207</v>
       </c>
-      <c r="N88" s="6">
-        <f>B88-H88</f>
+      <c r="O88" s="6">
+        <f>B88-I88</f>
         <v>0</v>
       </c>
-      <c r="O88" s="6">
-        <f>C88-I88</f>
+      <c r="P88" s="6">
+        <f>C88-J88</f>
         <v>0</v>
       </c>
-      <c r="P88" s="6">
-        <f>D88-J88</f>
+      <c r="Q88" s="6">
+        <f>D88-K88</f>
         <v>0</v>
       </c>
-      <c r="Q88" s="8"/>
       <c r="R88" s="8"/>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="G89" s="3"/>
-      <c r="I89" s="3"/>
+      <c r="S88" s="8"/>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="16"/>
+      <c r="H89" s="3"/>
       <c r="J89" s="3"/>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" t="s">
-        <v>102</v>
+      <c r="K89" s="3"/>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="B90" s="3">
         <v>91118514</v>
@@ -4030,45 +4079,45 @@
       <c r="F90" s="8">
         <v>3.21</v>
       </c>
-      <c r="G90" s="3"/>
-      <c r="H90" s="6">
-        <f>SUM(H70:H86)</f>
-        <v>91118564</v>
-      </c>
+      <c r="H90" s="3"/>
       <c r="I90" s="6">
         <f>SUM(I70:I86)</f>
-        <v>4056907</v>
+        <v>91118564</v>
       </c>
       <c r="J90" s="6">
         <f>SUM(J70:J86)</f>
+        <v>4056907</v>
+      </c>
+      <c r="K90" s="6">
+        <f>SUM(K70:K86)</f>
         <v>2838811</v>
       </c>
-      <c r="K90" s="13">
-        <f t="shared" ref="K90" si="14">100*C90/B90</f>
+      <c r="L90" s="13">
+        <f t="shared" ref="L90" si="14">100*C90/B90</f>
         <v>4.4380256245179766</v>
       </c>
-      <c r="L90" s="13">
-        <f t="shared" ref="L90" si="15">D90/B90*100</f>
+      <c r="M90" s="13">
+        <f t="shared" ref="M90" si="15">D90/B90*100</f>
         <v>3.1019360126966071</v>
       </c>
-      <c r="N90" s="6">
-        <f>B90-H90</f>
+      <c r="O90" s="6">
+        <f>B90-I90</f>
         <v>-50</v>
       </c>
-      <c r="O90" s="6">
-        <f>C90-I90</f>
+      <c r="P90" s="6">
+        <f>C90-J90</f>
         <v>-13044</v>
       </c>
-      <c r="P90" s="6">
-        <f>D90-J90</f>
+      <c r="Q90" s="6">
+        <f>D90-K90</f>
         <v>-12373</v>
       </c>
-      <c r="Q90" s="14">
-        <f t="shared" ref="Q90" si="16">E90-K90</f>
+      <c r="R90" s="14">
+        <f t="shared" ref="R90" si="16">E90-L90</f>
         <v>0.15197437548202331</v>
       </c>
-      <c r="R90" s="14">
-        <f t="shared" ref="R90" si="17">F90-L90</f>
+      <c r="S90" s="14">
+        <f t="shared" ref="S90" si="17">F90-M90</f>
         <v>0.10806398730339284</v>
       </c>
     </row>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1881.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1881.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476B1074-6EE1-47D7-B94C-49518827F45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6936CB07-0A10-4243-B1AE-0785C57AF587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="82620" yWindow="1380" windowWidth="20655" windowHeight="16800" activeTab="1" xr2:uid="{985C1713-17F3-42B8-B4A8-3581E02B593F}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{985C1713-17F3-42B8-B4A8-3581E02B593F}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="2" r:id="rId1"/>
@@ -252,9 +252,6 @@
     <t>чр YY</t>
   </si>
   <si>
-    <t>чс YY</t>
-  </si>
-  <si>
     <t>Вятская</t>
   </si>
   <si>
@@ -370,6 +367,9 @@
   </si>
   <si>
     <t>добавить к</t>
+  </si>
+  <si>
+    <t>чу YY</t>
   </si>
 </sst>
 </file>
@@ -782,43 +782,43 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
         <v>103</v>
-      </c>
-      <c r="D15" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -856,46 +856,46 @@
         <v>70</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="O1" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="R1" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="O1" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="R1" s="12" t="s">
+      <c r="S1" s="12" t="s">
         <v>94</v>
-      </c>
-      <c r="S1" s="12" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
@@ -1072,10 +1072,10 @@
         <v>11483</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="3"/>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" s="3">
         <v>2698500</v>
@@ -1567,7 +1567,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20" s="3">
         <v>765403</v>
@@ -1887,7 +1887,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B28" s="3">
         <v>1860787</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B29" s="3">
         <v>542237</v>
@@ -2447,7 +2447,7 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B42" s="3">
         <v>837928</v>
@@ -2647,7 +2647,7 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B47" s="3">
         <v>633725</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B52" s="3">
         <v>67173</v>
@@ -2987,7 +2987,7 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B56" s="3">
         <v>603174</v>
@@ -3428,7 +3428,7 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B67" s="3">
         <v>1875855</v>
@@ -3688,7 +3688,7 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75" s="3">
         <v>74000</v>
@@ -3736,22 +3736,22 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B77" s="3">
         <v>685945</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G77" s="9"/>
       <c r="H77" s="3"/>
@@ -3761,22 +3761,22 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B78" s="3">
         <v>1109542</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G78" s="9"/>
       <c r="H78" s="3"/>
@@ -3792,16 +3792,16 @@
         <v>320075</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G79" s="9"/>
       <c r="H79" s="3"/>
@@ -3841,16 +3841,16 @@
         <v>808000</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G81" s="9"/>
       <c r="H81" s="3"/>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B85" s="3">
         <v>23194</v>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B86" s="3">
         <v>28622</v>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B88" s="3">
         <f>SUM(B85:B86)</f>
@@ -4062,7 +4062,7 @@
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B90" s="3">
         <v>91118514</v>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1881.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1881.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6936CB07-0A10-4243-B1AE-0785C57AF587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4197B1C-0C75-4D23-94DF-E7BB0EB7F5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{985C1713-17F3-42B8-B4A8-3581E02B593F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="115">
   <si>
     <t>Архангельская</t>
   </si>
@@ -370,6 +370,18 @@
   </si>
   <si>
     <t>чу YY</t>
+  </si>
+  <si>
+    <t>Область войска Донского</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>Область войска Донского по "Статистический временник Российской Империи" 3.20 стр. 5</t>
+  </si>
+  <si>
+    <t>"Движение населения в Европейской России за 1881 год"</t>
   </si>
 </sst>
 </file>
@@ -429,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -463,6 +475,7 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -828,7 +841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3A086F-87DA-488B-9CB2-83FFAA408376}">
-  <dimension ref="A1:S90"/>
+  <dimension ref="A1:S99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="27.578125" customWidth="1"/>
@@ -4121,6 +4134,35 @@
         <v>0.10806398730339284</v>
       </c>
     </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" t="s">
+        <v>111</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C93" s="3">
+        <v>78503</v>
+      </c>
+      <c r="D93" s="3">
+        <v>41812</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
